--- a/artfynd/A 3056-2025 artfynd.xlsx
+++ b/artfynd/A 3056-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123273274</v>
+        <v>123273023</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kilåmyran, Kilåmyran, Ång</t>
+          <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582412</v>
+        <v>582467</v>
       </c>
       <c r="R2" t="n">
-        <v>7040588</v>
+        <v>7040628</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123273921</v>
+        <v>123273141</v>
       </c>
       <c r="B3" t="n">
-        <v>79847</v>
+        <v>57631</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +808,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kilåmyran, Kilåmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582380</v>
+        <v>582428</v>
       </c>
       <c r="R3" t="n">
-        <v>7040762</v>
+        <v>7040636</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +901,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123273924</v>
+        <v>123272562</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,34 +929,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kilåmyran, Kilåmyran, Ång</t>
+          <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582401</v>
+        <v>582561</v>
       </c>
       <c r="R4" t="n">
-        <v>7040750</v>
+        <v>7040646</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +1003,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123273006</v>
+        <v>123272584</v>
       </c>
       <c r="B5" t="n">
-        <v>56688</v>
+        <v>79847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,43 +1047,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582456</v>
+        <v>582561</v>
       </c>
       <c r="R5" t="n">
-        <v>7040629</v>
+        <v>7040650</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123272562</v>
+        <v>123272505</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,39 +1163,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582561</v>
+        <v>582557</v>
       </c>
       <c r="R6" t="n">
-        <v>7040646</v>
+        <v>7040639</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1222,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,12 +1232,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1259,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123273156</v>
+        <v>123273921</v>
       </c>
       <c r="B7" t="n">
-        <v>90970</v>
+        <v>79847</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,43 +1275,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bodmyran, Bodmyran, Ång</t>
+          <t>Kilåmyran, Kilåmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582431</v>
+        <v>582380</v>
       </c>
       <c r="R7" t="n">
-        <v>7040632</v>
+        <v>7040762</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123272584</v>
+        <v>123273924</v>
       </c>
       <c r="B8" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,34 +1387,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bodmyran, Bodmyran, Ång</t>
+          <t>Kilåmyran, Kilåmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582561</v>
+        <v>582401</v>
       </c>
       <c r="R8" t="n">
-        <v>7040650</v>
+        <v>7040750</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,10 +1483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123273141</v>
+        <v>123272744</v>
       </c>
       <c r="B9" t="n">
-        <v>57631</v>
+        <v>56688</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,47 +1495,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kilåmyran, Kilåmyran, Ång</t>
+          <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582428</v>
+        <v>582552</v>
       </c>
       <c r="R9" t="n">
-        <v>7040636</v>
+        <v>7040605</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1567,7 +1563,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1577,7 +1573,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1604,7 +1600,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123272505</v>
+        <v>123273274</v>
       </c>
       <c r="B10" t="n">
         <v>78766</v>
@@ -1640,14 +1636,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bodmyran, Bodmyran, Ång</t>
+          <t>Kilåmyran, Kilåmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582557</v>
+        <v>582412</v>
       </c>
       <c r="R10" t="n">
-        <v>7040639</v>
+        <v>7040588</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1679,7 +1675,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1689,7 +1685,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1716,10 +1712,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123273023</v>
+        <v>123273156</v>
       </c>
       <c r="B11" t="n">
-        <v>56688</v>
+        <v>90970</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1728,31 +1724,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1761,10 +1761,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582467</v>
+        <v>582431</v>
       </c>
       <c r="R11" t="n">
-        <v>7040628</v>
+        <v>7040632</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1833,7 +1833,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123272744</v>
+        <v>123273006</v>
       </c>
       <c r="B12" t="n">
         <v>56688</v>
@@ -1878,10 +1878,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582552</v>
+        <v>582456</v>
       </c>
       <c r="R12" t="n">
-        <v>7040605</v>
+        <v>7040629</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 3056-2025 artfynd.xlsx
+++ b/artfynd/A 3056-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123273023</v>
+        <v>123273156</v>
       </c>
       <c r="B2" t="n">
-        <v>56688</v>
+        <v>90970</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582467</v>
+        <v>582431</v>
       </c>
       <c r="R2" t="n">
-        <v>7040628</v>
+        <v>7040632</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123273141</v>
+        <v>123272744</v>
       </c>
       <c r="B3" t="n">
-        <v>57631</v>
+        <v>56688</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,47 +808,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kilåmyran, Kilåmyran, Ång</t>
+          <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582428</v>
+        <v>582552</v>
       </c>
       <c r="R3" t="n">
-        <v>7040636</v>
+        <v>7040605</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123272562</v>
+        <v>123273141</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,39 +929,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bodmyran, Bodmyran, Ång</t>
+          <t>Kilåmyran, Kilåmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582561</v>
+        <v>582428</v>
       </c>
       <c r="R4" t="n">
-        <v>7040646</v>
+        <v>7040636</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,12 +1007,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123272584</v>
+        <v>123273274</v>
       </c>
       <c r="B5" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,34 +1050,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bodmyran, Bodmyran, Ång</t>
+          <t>Kilåmyran, Kilåmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582561</v>
+        <v>582412</v>
       </c>
       <c r="R5" t="n">
-        <v>7040650</v>
+        <v>7040588</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1119,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123272505</v>
+        <v>123273921</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,34 +1162,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bodmyran, Bodmyran, Ång</t>
+          <t>Kilåmyran, Kilåmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582557</v>
+        <v>582380</v>
       </c>
       <c r="R6" t="n">
-        <v>7040639</v>
+        <v>7040762</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,22 +1246,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123273921</v>
+        <v>123273023</v>
       </c>
       <c r="B7" t="n">
-        <v>79847</v>
+        <v>56688</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,38 +1270,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kilåmyran, Kilåmyran, Ång</t>
+          <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582380</v>
+        <v>582467</v>
       </c>
       <c r="R7" t="n">
-        <v>7040762</v>
+        <v>7040628</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1334,7 +1338,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1348,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1483,7 +1487,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123272744</v>
+        <v>123273006</v>
       </c>
       <c r="B9" t="n">
         <v>56688</v>
@@ -1528,10 +1532,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582552</v>
+        <v>582456</v>
       </c>
       <c r="R9" t="n">
-        <v>7040605</v>
+        <v>7040629</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,7 +1567,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1573,7 +1577,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,7 +1604,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123273274</v>
+        <v>123272505</v>
       </c>
       <c r="B10" t="n">
         <v>78766</v>
@@ -1636,14 +1640,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kilåmyran, Kilåmyran, Ång</t>
+          <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582412</v>
+        <v>582557</v>
       </c>
       <c r="R10" t="n">
-        <v>7040588</v>
+        <v>7040639</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1675,7 +1679,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1685,7 +1689,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1712,10 +1716,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123273156</v>
+        <v>123272584</v>
       </c>
       <c r="B11" t="n">
-        <v>90970</v>
+        <v>79847</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1728,43 +1732,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582431</v>
+        <v>582561</v>
       </c>
       <c r="R11" t="n">
-        <v>7040632</v>
+        <v>7040650</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1796,7 +1791,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1806,7 +1801,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1821,22 +1816,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123273006</v>
+        <v>123272562</v>
       </c>
       <c r="B12" t="n">
-        <v>56688</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1845,31 +1840,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1878,10 +1873,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582456</v>
+        <v>582561</v>
       </c>
       <c r="R12" t="n">
-        <v>7040629</v>
+        <v>7040646</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1913,7 +1908,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1923,7 +1918,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 3056-2025 artfynd.xlsx
+++ b/artfynd/A 3056-2025 artfynd.xlsx
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123273141</v>
+        <v>123273274</v>
       </c>
       <c r="B4" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,43 +929,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kilåmyran, Kilåmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582428</v>
+        <v>582412</v>
       </c>
       <c r="R4" t="n">
-        <v>7040636</v>
+        <v>7040588</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123273274</v>
+        <v>123273921</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,21 +1041,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1074,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582412</v>
+        <v>582380</v>
       </c>
       <c r="R5" t="n">
-        <v>7040588</v>
+        <v>7040762</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,22 +1125,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123273921</v>
+        <v>123273141</v>
       </c>
       <c r="B6" t="n">
-        <v>79847</v>
+        <v>57631</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,34 +1153,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kilåmyran, Kilåmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582380</v>
+        <v>582428</v>
       </c>
       <c r="R6" t="n">
-        <v>7040762</v>
+        <v>7040636</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,12 +1246,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 3056-2025 artfynd.xlsx
+++ b/artfynd/A 3056-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123273156</v>
       </c>
       <c r="B2" t="n">
-        <v>90970</v>
+        <v>90973</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>123272744</v>
       </c>
       <c r="B3" t="n">
-        <v>56688</v>
+        <v>56691</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123273274</v>
+        <v>123273023</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>56691</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,38 +925,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kilåmyran, Kilåmyran, Ång</t>
+          <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582412</v>
+        <v>582467</v>
       </c>
       <c r="R4" t="n">
-        <v>7040588</v>
+        <v>7040628</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,22 +1018,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123273921</v>
+        <v>123272584</v>
       </c>
       <c r="B5" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1061,14 +1066,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kilåmyran, Kilåmyran, Ång</t>
+          <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582380</v>
+        <v>582561</v>
       </c>
       <c r="R5" t="n">
-        <v>7040762</v>
+        <v>7040650</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,22 +1130,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123273141</v>
+        <v>123273924</v>
       </c>
       <c r="B6" t="n">
-        <v>57631</v>
+        <v>78769</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,43 +1158,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kilåmyran, Kilåmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582428</v>
+        <v>582401</v>
       </c>
       <c r="R6" t="n">
-        <v>7040636</v>
+        <v>7040750</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,10 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123273023</v>
+        <v>123273274</v>
       </c>
       <c r="B7" t="n">
-        <v>56688</v>
+        <v>78769</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,43 +1266,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bodmyran, Bodmyran, Ång</t>
+          <t>Kilåmyran, Kilåmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582467</v>
+        <v>582412</v>
       </c>
       <c r="R7" t="n">
-        <v>7040628</v>
+        <v>7040588</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,7 +1329,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1348,7 +1339,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,22 +1354,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123273924</v>
+        <v>123273921</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>79850</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1391,21 +1382,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1415,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582401</v>
+        <v>582380</v>
       </c>
       <c r="R8" t="n">
-        <v>7040750</v>
+        <v>7040762</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1460,7 +1451,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,12 +1466,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1490,7 +1481,7 @@
         <v>123273006</v>
       </c>
       <c r="B9" t="n">
-        <v>56688</v>
+        <v>56691</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1607,7 +1598,7 @@
         <v>123272505</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1716,10 +1707,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123272584</v>
+        <v>123272562</v>
       </c>
       <c r="B11" t="n">
-        <v>79847</v>
+        <v>57481</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1732,24 +1723,29 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bodmyran, Bodmyran, Ång</t>
@@ -1759,7 +1755,7 @@
         <v>582561</v>
       </c>
       <c r="R11" t="n">
-        <v>7040650</v>
+        <v>7040646</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1791,7 +1787,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1801,7 +1797,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1828,10 +1829,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123272562</v>
+        <v>123273141</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>57634</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1844,39 +1845,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bodmyran, Bodmyran, Ång</t>
+          <t>Kilåmyran, Kilåmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582561</v>
+        <v>582428</v>
       </c>
       <c r="R12" t="n">
-        <v>7040646</v>
+        <v>7040636</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1908,7 +1913,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1918,12 +1923,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 3056-2025 artfynd.xlsx
+++ b/artfynd/A 3056-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123273156</v>
+        <v>123273006</v>
       </c>
       <c r="B2" t="n">
-        <v>90973</v>
+        <v>56691</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582431</v>
+        <v>582456</v>
       </c>
       <c r="R2" t="n">
-        <v>7040632</v>
+        <v>7040629</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123272744</v>
+        <v>123272562</v>
       </c>
       <c r="B3" t="n">
-        <v>56691</v>
+        <v>57481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,31 +804,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -841,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582552</v>
+        <v>582561</v>
       </c>
       <c r="R3" t="n">
-        <v>7040605</v>
+        <v>7040646</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +882,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123273023</v>
+        <v>123272505</v>
       </c>
       <c r="B4" t="n">
-        <v>56691</v>
+        <v>78771</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,43 +926,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582467</v>
+        <v>582557</v>
       </c>
       <c r="R4" t="n">
-        <v>7040628</v>
+        <v>7040639</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,22 +1014,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123272584</v>
+        <v>123273156</v>
       </c>
       <c r="B5" t="n">
-        <v>79850</v>
+        <v>90975</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,34 +1042,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582561</v>
+        <v>582431</v>
       </c>
       <c r="R5" t="n">
-        <v>7040650</v>
+        <v>7040632</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,12 +1135,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1145,7 +1150,7 @@
         <v>123273924</v>
       </c>
       <c r="B6" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1254,10 +1259,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123273274</v>
+        <v>123272584</v>
       </c>
       <c r="B7" t="n">
-        <v>78769</v>
+        <v>79852</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,34 +1275,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kilåmyran, Kilåmyran, Ång</t>
+          <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582412</v>
+        <v>582561</v>
       </c>
       <c r="R7" t="n">
-        <v>7040588</v>
+        <v>7040650</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,7 +1344,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123273921</v>
+        <v>123273023</v>
       </c>
       <c r="B8" t="n">
-        <v>79850</v>
+        <v>56691</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,38 +1383,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kilåmyran, Kilåmyran, Ång</t>
+          <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582380</v>
+        <v>582467</v>
       </c>
       <c r="R8" t="n">
-        <v>7040762</v>
+        <v>7040628</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1441,7 +1451,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,7 +1461,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123273006</v>
+        <v>123273274</v>
       </c>
       <c r="B9" t="n">
-        <v>56691</v>
+        <v>78771</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,43 +1500,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bodmyran, Bodmyran, Ång</t>
+          <t>Kilåmyran, Kilåmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582456</v>
+        <v>582412</v>
       </c>
       <c r="R9" t="n">
-        <v>7040629</v>
+        <v>7040588</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,7 +1563,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1568,7 +1573,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,10 +1600,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123272505</v>
+        <v>123272744</v>
       </c>
       <c r="B10" t="n">
-        <v>78769</v>
+        <v>56691</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,38 +1612,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582557</v>
+        <v>582552</v>
       </c>
       <c r="R10" t="n">
-        <v>7040639</v>
+        <v>7040605</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1670,7 +1680,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1680,7 +1690,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1707,10 +1717,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123272562</v>
+        <v>123273141</v>
       </c>
       <c r="B11" t="n">
-        <v>57481</v>
+        <v>57634</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1723,39 +1733,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bodmyran, Bodmyran, Ång</t>
+          <t>Kilåmyran, Kilåmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582561</v>
+        <v>582428</v>
       </c>
       <c r="R11" t="n">
-        <v>7040646</v>
+        <v>7040636</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1787,7 +1801,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1797,12 +1811,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1829,10 +1838,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123273141</v>
+        <v>123273921</v>
       </c>
       <c r="B12" t="n">
-        <v>57634</v>
+        <v>79852</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1845,43 +1854,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kilåmyran, Kilåmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582428</v>
+        <v>582380</v>
       </c>
       <c r="R12" t="n">
-        <v>7040636</v>
+        <v>7040762</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1938,12 +1938,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 3056-2025 artfynd.xlsx
+++ b/artfynd/A 3056-2025 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123272562</v>
+        <v>123273023</v>
       </c>
       <c r="B3" t="n">
-        <v>57481</v>
+        <v>56691</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,31 +804,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582561</v>
+        <v>582467</v>
       </c>
       <c r="R3" t="n">
-        <v>7040646</v>
+        <v>7040628</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,12 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,22 +897,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123272505</v>
+        <v>123273924</v>
       </c>
       <c r="B4" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -950,14 +945,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bodmyran, Bodmyran, Ång</t>
+          <t>Kilåmyran, Kilåmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582557</v>
+        <v>582401</v>
       </c>
       <c r="R4" t="n">
-        <v>7040639</v>
+        <v>7040750</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123273156</v>
+        <v>123273141</v>
       </c>
       <c r="B5" t="n">
-        <v>90975</v>
+        <v>57634</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,43 +1037,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bodmyran, Bodmyran, Ång</t>
+          <t>Kilåmyran, Kilåmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582431</v>
+        <v>582428</v>
       </c>
       <c r="R5" t="n">
-        <v>7040632</v>
+        <v>7040636</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,22 +1130,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123273924</v>
+        <v>123272562</v>
       </c>
       <c r="B6" t="n">
-        <v>78771</v>
+        <v>57481</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,34 +1158,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kilåmyran, Kilåmyran, Ång</t>
+          <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582401</v>
+        <v>582561</v>
       </c>
       <c r="R6" t="n">
-        <v>7040750</v>
+        <v>7040646</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,7 +1232,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,10 +1264,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123272584</v>
+        <v>123272744</v>
       </c>
       <c r="B7" t="n">
-        <v>79852</v>
+        <v>56691</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,38 +1276,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582561</v>
+        <v>582552</v>
       </c>
       <c r="R7" t="n">
-        <v>7040650</v>
+        <v>7040605</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1334,7 +1344,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1354,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123273023</v>
+        <v>123272584</v>
       </c>
       <c r="B8" t="n">
-        <v>56691</v>
+        <v>79853</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,43 +1393,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582467</v>
+        <v>582561</v>
       </c>
       <c r="R8" t="n">
-        <v>7040628</v>
+        <v>7040650</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,7 +1456,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1461,7 +1466,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1476,22 +1481,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123273274</v>
+        <v>123272505</v>
       </c>
       <c r="B9" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1524,14 +1529,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kilåmyran, Kilåmyran, Ång</t>
+          <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582412</v>
+        <v>582557</v>
       </c>
       <c r="R9" t="n">
-        <v>7040588</v>
+        <v>7040639</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,7 +1568,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1573,7 +1578,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,10 +1605,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123272744</v>
+        <v>123273274</v>
       </c>
       <c r="B10" t="n">
-        <v>56691</v>
+        <v>78772</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,43 +1617,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bodmyran, Bodmyran, Ång</t>
+          <t>Kilåmyran, Kilåmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582552</v>
+        <v>582412</v>
       </c>
       <c r="R10" t="n">
-        <v>7040605</v>
+        <v>7040588</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1717,10 +1717,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123273141</v>
+        <v>123273921</v>
       </c>
       <c r="B11" t="n">
-        <v>57634</v>
+        <v>79853</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1733,43 +1733,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kilåmyran, Kilåmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582428</v>
+        <v>582380</v>
       </c>
       <c r="R11" t="n">
-        <v>7040636</v>
+        <v>7040762</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1801,7 +1792,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1811,7 +1802,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1826,22 +1817,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123273921</v>
+        <v>123273156</v>
       </c>
       <c r="B12" t="n">
-        <v>79852</v>
+        <v>90981</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1854,34 +1845,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kilåmyran, Kilåmyran, Ång</t>
+          <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582380</v>
+        <v>582431</v>
       </c>
       <c r="R12" t="n">
-        <v>7040762</v>
+        <v>7040632</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 3056-2025 artfynd.xlsx
+++ b/artfynd/A 3056-2025 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123273023</v>
+        <v>123273921</v>
       </c>
       <c r="B4" t="n">
-        <v>56691</v>
+        <v>79856</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,43 +921,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bodmyran, Bodmyran, Ång</t>
+          <t>Kilåmyran, Kilåmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582467</v>
+        <v>582380</v>
       </c>
       <c r="R4" t="n">
-        <v>7040628</v>
+        <v>7040762</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123273921</v>
+        <v>123273924</v>
       </c>
       <c r="B5" t="n">
-        <v>79856</v>
+        <v>78775</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1037,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582380</v>
+        <v>582401</v>
       </c>
       <c r="R5" t="n">
-        <v>7040762</v>
+        <v>7040750</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,22 +1121,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123273924</v>
+        <v>123273023</v>
       </c>
       <c r="B6" t="n">
-        <v>78775</v>
+        <v>56691</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,38 +1145,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kilåmyran, Kilåmyran, Ång</t>
+          <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582401</v>
+        <v>582467</v>
       </c>
       <c r="R6" t="n">
-        <v>7040750</v>
+        <v>7040628</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,12 +1238,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 3056-2025 artfynd.xlsx
+++ b/artfynd/A 3056-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123272744</v>
+        <v>123273921</v>
       </c>
       <c r="B2" t="n">
-        <v>56691</v>
+        <v>79862</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bodmyran, Bodmyran, Ång</t>
+          <t>Kilåmyran, Kilåmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582552</v>
+        <v>582380</v>
       </c>
       <c r="R2" t="n">
-        <v>7040605</v>
+        <v>7040762</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,12 +775,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -795,7 +790,7 @@
         <v>123273006</v>
       </c>
       <c r="B3" t="n">
-        <v>56691</v>
+        <v>56697</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -909,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123273921</v>
+        <v>123273141</v>
       </c>
       <c r="B4" t="n">
-        <v>79856</v>
+        <v>57640</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,34 +920,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kilåmyran, Kilåmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582380</v>
+        <v>582428</v>
       </c>
       <c r="R4" t="n">
-        <v>7040762</v>
+        <v>7040636</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,12 +1013,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1024,7 +1028,7 @@
         <v>123273924</v>
       </c>
       <c r="B5" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1133,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123273023</v>
+        <v>123272505</v>
       </c>
       <c r="B6" t="n">
-        <v>56691</v>
+        <v>78781</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,43 +1149,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582467</v>
+        <v>582557</v>
       </c>
       <c r="R6" t="n">
-        <v>7040628</v>
+        <v>7040639</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,12 +1237,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1253,7 +1252,7 @@
         <v>123273156</v>
       </c>
       <c r="B7" t="n">
-        <v>90984</v>
+        <v>91001</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1374,7 +1373,7 @@
         <v>123273274</v>
       </c>
       <c r="B8" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1486,7 +1485,7 @@
         <v>123272562</v>
       </c>
       <c r="B9" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1605,10 +1604,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123273141</v>
+        <v>123273023</v>
       </c>
       <c r="B10" t="n">
-        <v>57634</v>
+        <v>56697</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1617,47 +1616,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kilåmyran, Kilåmyran, Ång</t>
+          <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582428</v>
+        <v>582467</v>
       </c>
       <c r="R10" t="n">
-        <v>7040636</v>
+        <v>7040628</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1689,7 +1684,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1699,7 +1694,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1714,12 +1709,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1729,7 +1724,7 @@
         <v>123272584</v>
       </c>
       <c r="B11" t="n">
-        <v>79856</v>
+        <v>79862</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1838,10 +1833,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123272505</v>
+        <v>123272744</v>
       </c>
       <c r="B12" t="n">
-        <v>78775</v>
+        <v>56697</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1850,38 +1845,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582557</v>
+        <v>582552</v>
       </c>
       <c r="R12" t="n">
-        <v>7040639</v>
+        <v>7040605</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 3056-2025 artfynd.xlsx
+++ b/artfynd/A 3056-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123273921</v>
+        <v>123273006</v>
       </c>
       <c r="B2" t="n">
-        <v>79862</v>
+        <v>56697</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kilåmyran, Kilåmyran, Ång</t>
+          <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582380</v>
+        <v>582456</v>
       </c>
       <c r="R2" t="n">
-        <v>7040762</v>
+        <v>7040629</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123273006</v>
+        <v>123273921</v>
       </c>
       <c r="B3" t="n">
-        <v>56697</v>
+        <v>79862</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,43 +804,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bodmyran, Bodmyran, Ång</t>
+          <t>Kilåmyran, Kilåmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582456</v>
+        <v>582380</v>
       </c>
       <c r="R3" t="n">
-        <v>7040629</v>
+        <v>7040762</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,12 +892,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 3056-2025 artfynd.xlsx
+++ b/artfynd/A 3056-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123273006</v>
+        <v>123273921</v>
       </c>
       <c r="B2" t="n">
-        <v>56697</v>
+        <v>79862</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bodmyran, Bodmyran, Ång</t>
+          <t>Kilåmyran, Kilåmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582456</v>
+        <v>582380</v>
       </c>
       <c r="R2" t="n">
-        <v>7040629</v>
+        <v>7040762</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123273921</v>
+        <v>123273006</v>
       </c>
       <c r="B3" t="n">
-        <v>79862</v>
+        <v>56697</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,38 +799,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kilåmyran, Kilåmyran, Ång</t>
+          <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582380</v>
+        <v>582456</v>
       </c>
       <c r="R3" t="n">
-        <v>7040762</v>
+        <v>7040629</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,12 +892,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 3056-2025 artfynd.xlsx
+++ b/artfynd/A 3056-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123273921</v>
+        <v>123272584</v>
       </c>
       <c r="B2" t="n">
-        <v>79862</v>
+        <v>79867</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kilåmyran, Kilåmyran, Ång</t>
+          <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582380</v>
+        <v>582561</v>
       </c>
       <c r="R2" t="n">
-        <v>7040762</v>
+        <v>7040650</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123273006</v>
+        <v>123273924</v>
       </c>
       <c r="B3" t="n">
-        <v>56697</v>
+        <v>78786</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,43 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bodmyran, Bodmyran, Ång</t>
+          <t>Kilåmyran, Kilåmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582456</v>
+        <v>582401</v>
       </c>
       <c r="R3" t="n">
-        <v>7040629</v>
+        <v>7040750</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123273141</v>
+        <v>123273921</v>
       </c>
       <c r="B4" t="n">
-        <v>57640</v>
+        <v>79867</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,43 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kilåmyran, Kilåmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582428</v>
+        <v>582380</v>
       </c>
       <c r="R4" t="n">
-        <v>7040636</v>
+        <v>7040762</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,22 +999,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123273924</v>
+        <v>123273274</v>
       </c>
       <c r="B5" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1065,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582401</v>
+        <v>582412</v>
       </c>
       <c r="R5" t="n">
-        <v>7040750</v>
+        <v>7040588</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123272505</v>
+        <v>123273156</v>
       </c>
       <c r="B6" t="n">
-        <v>78781</v>
+        <v>91006</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,34 +1139,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582557</v>
+        <v>582431</v>
       </c>
       <c r="R6" t="n">
-        <v>7040639</v>
+        <v>7040632</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,22 +1232,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123273156</v>
+        <v>123273141</v>
       </c>
       <c r="B7" t="n">
-        <v>91001</v>
+        <v>57643</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,43 +1260,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bodmyran, Bodmyran, Ång</t>
+          <t>Kilåmyran, Kilåmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582431</v>
+        <v>582428</v>
       </c>
       <c r="R7" t="n">
-        <v>7040632</v>
+        <v>7040636</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1343,7 +1338,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1358,22 +1353,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123273274</v>
+        <v>123272744</v>
       </c>
       <c r="B8" t="n">
-        <v>78781</v>
+        <v>56700</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,38 +1377,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kilåmyran, Kilåmyran, Ång</t>
+          <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582412</v>
+        <v>582552</v>
       </c>
       <c r="R8" t="n">
-        <v>7040588</v>
+        <v>7040605</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123272562</v>
+        <v>123273006</v>
       </c>
       <c r="B9" t="n">
-        <v>57487</v>
+        <v>56700</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,31 +1494,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1527,10 +1527,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582561</v>
+        <v>582456</v>
       </c>
       <c r="R9" t="n">
-        <v>7040646</v>
+        <v>7040629</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,12 +1572,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1607,7 +1602,7 @@
         <v>123273023</v>
       </c>
       <c r="B10" t="n">
-        <v>56697</v>
+        <v>56700</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1721,10 +1716,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123272584</v>
+        <v>123272562</v>
       </c>
       <c r="B11" t="n">
-        <v>79862</v>
+        <v>57490</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1737,24 +1732,29 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bodmyran, Bodmyran, Ång</t>
@@ -1764,7 +1764,7 @@
         <v>582561</v>
       </c>
       <c r="R11" t="n">
-        <v>7040650</v>
+        <v>7040646</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1806,7 +1806,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1833,10 +1838,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123272744</v>
+        <v>123272505</v>
       </c>
       <c r="B12" t="n">
-        <v>56697</v>
+        <v>78786</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1845,43 +1850,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582552</v>
+        <v>582557</v>
       </c>
       <c r="R12" t="n">
-        <v>7040605</v>
+        <v>7040639</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 3056-2025 artfynd.xlsx
+++ b/artfynd/A 3056-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123272584</v>
+        <v>123273924</v>
       </c>
       <c r="B2" t="n">
-        <v>79867</v>
+        <v>78788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bodmyran, Bodmyran, Ång</t>
+          <t>Kilåmyran, Kilåmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582561</v>
+        <v>582401</v>
       </c>
       <c r="R2" t="n">
-        <v>7040650</v>
+        <v>7040750</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123273924</v>
+        <v>123273023</v>
       </c>
       <c r="B3" t="n">
-        <v>78786</v>
+        <v>56700</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,38 +799,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kilåmyran, Kilåmyran, Ång</t>
+          <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582401</v>
+        <v>582467</v>
       </c>
       <c r="R3" t="n">
-        <v>7040750</v>
+        <v>7040628</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,12 +892,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -902,7 +907,7 @@
         <v>123273921</v>
       </c>
       <c r="B4" t="n">
-        <v>79867</v>
+        <v>79869</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1011,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123273274</v>
+        <v>123273006</v>
       </c>
       <c r="B5" t="n">
-        <v>78786</v>
+        <v>56700</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,38 +1028,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kilåmyran, Kilåmyran, Ång</t>
+          <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582412</v>
+        <v>582456</v>
       </c>
       <c r="R5" t="n">
-        <v>7040588</v>
+        <v>7040629</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,7 +1136,7 @@
         <v>123273156</v>
       </c>
       <c r="B6" t="n">
-        <v>91006</v>
+        <v>91008</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1247,7 +1257,7 @@
         <v>123273141</v>
       </c>
       <c r="B7" t="n">
-        <v>57643</v>
+        <v>57644</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1365,10 +1375,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123272744</v>
+        <v>123273274</v>
       </c>
       <c r="B8" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,43 +1387,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bodmyran, Bodmyran, Ång</t>
+          <t>Kilåmyran, Kilåmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582552</v>
+        <v>582412</v>
       </c>
       <c r="R8" t="n">
-        <v>7040605</v>
+        <v>7040588</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1445,7 +1450,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1455,7 +1460,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123273006</v>
+        <v>123272505</v>
       </c>
       <c r="B9" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,43 +1499,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582456</v>
+        <v>582557</v>
       </c>
       <c r="R9" t="n">
-        <v>7040629</v>
+        <v>7040639</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1599,7 +1599,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123273023</v>
+        <v>123272744</v>
       </c>
       <c r="B10" t="n">
         <v>56700</v>
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582467</v>
+        <v>582552</v>
       </c>
       <c r="R10" t="n">
-        <v>7040628</v>
+        <v>7040605</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1704,22 +1704,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123272562</v>
+        <v>123272584</v>
       </c>
       <c r="B11" t="n">
-        <v>57490</v>
+        <v>79869</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1732,29 +1732,24 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bodmyran, Bodmyran, Ång</t>
@@ -1764,7 +1759,7 @@
         <v>582561</v>
       </c>
       <c r="R11" t="n">
-        <v>7040646</v>
+        <v>7040650</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1796,7 +1791,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1806,12 +1801,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1838,10 +1828,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123272505</v>
+        <v>123272562</v>
       </c>
       <c r="B12" t="n">
-        <v>78786</v>
+        <v>57491</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1854,34 +1844,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582557</v>
+        <v>582561</v>
       </c>
       <c r="R12" t="n">
-        <v>7040639</v>
+        <v>7040646</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1913,7 +1908,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1923,7 +1918,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 3056-2025 artfynd.xlsx
+++ b/artfynd/A 3056-2025 artfynd.xlsx
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123273921</v>
+        <v>123273156</v>
       </c>
       <c r="B4" t="n">
-        <v>79869</v>
+        <v>91008</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,34 +920,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kilåmyran, Kilåmyran, Ång</t>
+          <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582380</v>
+        <v>582431</v>
       </c>
       <c r="R4" t="n">
-        <v>7040762</v>
+        <v>7040632</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123273006</v>
+        <v>123273921</v>
       </c>
       <c r="B5" t="n">
-        <v>56700</v>
+        <v>79869</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,43 +1037,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bodmyran, Bodmyran, Ång</t>
+          <t>Kilåmyran, Kilåmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582456</v>
+        <v>582380</v>
       </c>
       <c r="R5" t="n">
-        <v>7040629</v>
+        <v>7040762</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,22 +1125,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123273156</v>
+        <v>123273006</v>
       </c>
       <c r="B6" t="n">
-        <v>91008</v>
+        <v>56700</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,35 +1149,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582431</v>
+        <v>582456</v>
       </c>
       <c r="R6" t="n">
-        <v>7040632</v>
+        <v>7040629</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1242,12 +1242,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 3056-2025 artfynd.xlsx
+++ b/artfynd/A 3056-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123273924</v>
+        <v>123272744</v>
       </c>
       <c r="B2" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kilåmyran, Kilåmyran, Ång</t>
+          <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582401</v>
+        <v>582552</v>
       </c>
       <c r="R2" t="n">
-        <v>7040750</v>
+        <v>7040605</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -904,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123273156</v>
+        <v>123273924</v>
       </c>
       <c r="B4" t="n">
-        <v>91008</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,43 +925,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bodmyran, Bodmyran, Ång</t>
+          <t>Kilåmyran, Kilåmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582431</v>
+        <v>582401</v>
       </c>
       <c r="R4" t="n">
-        <v>7040632</v>
+        <v>7040750</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,22 +1009,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123273921</v>
+        <v>123273274</v>
       </c>
       <c r="B5" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,21 +1037,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1065,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582380</v>
+        <v>582412</v>
       </c>
       <c r="R5" t="n">
-        <v>7040762</v>
+        <v>7040588</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,22 +1121,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123273006</v>
+        <v>123272584</v>
       </c>
       <c r="B6" t="n">
-        <v>56700</v>
+        <v>79869</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,43 +1145,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582456</v>
+        <v>582561</v>
       </c>
       <c r="R6" t="n">
-        <v>7040629</v>
+        <v>7040650</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123273141</v>
+        <v>123272562</v>
       </c>
       <c r="B7" t="n">
-        <v>57644</v>
+        <v>57491</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,43 +1261,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kilåmyran, Kilåmyran, Ång</t>
+          <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582428</v>
+        <v>582561</v>
       </c>
       <c r="R7" t="n">
-        <v>7040636</v>
+        <v>7040646</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1348,7 +1335,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,7 +1367,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123273274</v>
+        <v>123272505</v>
       </c>
       <c r="B8" t="n">
         <v>78788</v>
@@ -1411,14 +1403,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kilåmyran, Kilåmyran, Ång</t>
+          <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582412</v>
+        <v>582557</v>
       </c>
       <c r="R8" t="n">
-        <v>7040588</v>
+        <v>7040639</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1460,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123272505</v>
+        <v>123273141</v>
       </c>
       <c r="B9" t="n">
-        <v>78788</v>
+        <v>57644</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,34 +1495,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bodmyran, Bodmyran, Ång</t>
+          <t>Kilåmyran, Kilåmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582557</v>
+        <v>582428</v>
       </c>
       <c r="R9" t="n">
-        <v>7040639</v>
+        <v>7040636</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,7 +1563,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1573,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1599,7 +1600,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123272744</v>
+        <v>123273006</v>
       </c>
       <c r="B10" t="n">
         <v>56700</v>
@@ -1644,10 +1645,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582552</v>
+        <v>582456</v>
       </c>
       <c r="R10" t="n">
-        <v>7040605</v>
+        <v>7040629</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1679,7 +1680,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1689,7 +1690,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1716,10 +1717,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123272584</v>
+        <v>123273156</v>
       </c>
       <c r="B11" t="n">
-        <v>79869</v>
+        <v>91008</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1732,34 +1733,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582561</v>
+        <v>582431</v>
       </c>
       <c r="R11" t="n">
-        <v>7040650</v>
+        <v>7040632</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1791,7 +1801,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1801,7 +1811,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1816,22 +1826,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123272562</v>
+        <v>123273921</v>
       </c>
       <c r="B12" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1844,39 +1854,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bodmyran, Bodmyran, Ång</t>
+          <t>Kilåmyran, Kilåmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582561</v>
+        <v>582380</v>
       </c>
       <c r="R12" t="n">
-        <v>7040646</v>
+        <v>7040762</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1908,7 +1913,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1918,12 +1923,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1938,12 +1938,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 3056-2025 artfynd.xlsx
+++ b/artfynd/A 3056-2025 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123273023</v>
+        <v>123272505</v>
       </c>
       <c r="B3" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,43 +804,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582467</v>
+        <v>582557</v>
       </c>
       <c r="R3" t="n">
-        <v>7040628</v>
+        <v>7040639</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,19 +892,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123273924</v>
+        <v>123273274</v>
       </c>
       <c r="B4" t="n">
         <v>78788</v>
@@ -949,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582401</v>
+        <v>582412</v>
       </c>
       <c r="R4" t="n">
-        <v>7040750</v>
+        <v>7040588</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123273274</v>
+        <v>123272562</v>
       </c>
       <c r="B5" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,34 +1032,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kilåmyran, Kilåmyran, Ång</t>
+          <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582412</v>
+        <v>582561</v>
       </c>
       <c r="R5" t="n">
-        <v>7040588</v>
+        <v>7040646</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123272584</v>
+        <v>123273141</v>
       </c>
       <c r="B6" t="n">
-        <v>79869</v>
+        <v>57644</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,34 +1154,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bodmyran, Bodmyran, Ång</t>
+          <t>Kilåmyran, Kilåmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582561</v>
+        <v>582428</v>
       </c>
       <c r="R6" t="n">
-        <v>7040650</v>
+        <v>7040636</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1222,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1232,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1259,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123272562</v>
+        <v>123273924</v>
       </c>
       <c r="B7" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,39 +1275,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bodmyran, Bodmyran, Ång</t>
+          <t>Kilåmyran, Kilåmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582561</v>
+        <v>582401</v>
       </c>
       <c r="R7" t="n">
-        <v>7040646</v>
+        <v>7040750</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,12 +1344,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123272505</v>
+        <v>123273156</v>
       </c>
       <c r="B8" t="n">
-        <v>78788</v>
+        <v>91008</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,34 +1387,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582557</v>
+        <v>582431</v>
       </c>
       <c r="R8" t="n">
-        <v>7040639</v>
+        <v>7040632</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1455,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1465,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,22 +1480,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123273141</v>
+        <v>123273023</v>
       </c>
       <c r="B9" t="n">
-        <v>57644</v>
+        <v>56700</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1491,47 +1504,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kilåmyran, Kilåmyran, Ång</t>
+          <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582428</v>
+        <v>582467</v>
       </c>
       <c r="R9" t="n">
-        <v>7040636</v>
+        <v>7040628</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,7 +1572,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1573,7 +1582,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1588,22 +1597,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123273006</v>
+        <v>123273921</v>
       </c>
       <c r="B10" t="n">
-        <v>56700</v>
+        <v>79869</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,43 +1621,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bodmyran, Bodmyran, Ång</t>
+          <t>Kilåmyran, Kilåmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582456</v>
+        <v>582380</v>
       </c>
       <c r="R10" t="n">
-        <v>7040629</v>
+        <v>7040762</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1680,7 +1684,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1690,7 +1694,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1705,22 +1709,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123273156</v>
+        <v>123273006</v>
       </c>
       <c r="B11" t="n">
-        <v>91008</v>
+        <v>56700</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1729,35 +1733,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1766,10 +1766,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582431</v>
+        <v>582456</v>
       </c>
       <c r="R11" t="n">
-        <v>7040632</v>
+        <v>7040629</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1826,19 +1826,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123273921</v>
+        <v>123272584</v>
       </c>
       <c r="B12" t="n">
         <v>79869</v>
@@ -1874,14 +1874,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kilåmyran, Kilåmyran, Ång</t>
+          <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582380</v>
+        <v>582561</v>
       </c>
       <c r="R12" t="n">
-        <v>7040762</v>
+        <v>7040650</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1938,12 +1938,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 3056-2025 artfynd.xlsx
+++ b/artfynd/A 3056-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123272744</v>
+        <v>123272584</v>
       </c>
       <c r="B2" t="n">
-        <v>56700</v>
+        <v>79869</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582552</v>
+        <v>582561</v>
       </c>
       <c r="R2" t="n">
-        <v>7040605</v>
+        <v>7040650</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123272505</v>
+        <v>123272744</v>
       </c>
       <c r="B3" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,38 +799,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582557</v>
+        <v>582552</v>
       </c>
       <c r="R3" t="n">
-        <v>7040639</v>
+        <v>7040605</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123273274</v>
+        <v>123272505</v>
       </c>
       <c r="B4" t="n">
         <v>78788</v>
@@ -940,14 +940,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kilåmyran, Kilåmyran, Ång</t>
+          <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582412</v>
+        <v>582557</v>
       </c>
       <c r="R4" t="n">
-        <v>7040588</v>
+        <v>7040639</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123272562</v>
+        <v>123273023</v>
       </c>
       <c r="B5" t="n">
-        <v>57491</v>
+        <v>56700</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,31 +1028,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582561</v>
+        <v>582467</v>
       </c>
       <c r="R5" t="n">
-        <v>7040646</v>
+        <v>7040628</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,12 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,22 +1121,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123273141</v>
+        <v>123273274</v>
       </c>
       <c r="B6" t="n">
-        <v>57644</v>
+        <v>78788</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,43 +1149,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kilåmyran, Kilåmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582428</v>
+        <v>582412</v>
       </c>
       <c r="R6" t="n">
-        <v>7040636</v>
+        <v>7040588</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123273924</v>
+        <v>123273921</v>
       </c>
       <c r="B7" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,21 +1261,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1299,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582401</v>
+        <v>582380</v>
       </c>
       <c r="R7" t="n">
-        <v>7040750</v>
+        <v>7040762</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1334,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,12 +1345,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1492,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123273023</v>
+        <v>123273141</v>
       </c>
       <c r="B9" t="n">
-        <v>56700</v>
+        <v>57644</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1504,43 +1490,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bodmyran, Bodmyran, Ång</t>
+          <t>Kilåmyran, Kilåmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582467</v>
+        <v>582428</v>
       </c>
       <c r="R9" t="n">
-        <v>7040628</v>
+        <v>7040636</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1572,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1582,7 +1572,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1597,22 +1587,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123273921</v>
+        <v>123272562</v>
       </c>
       <c r="B10" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1625,34 +1615,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kilåmyran, Kilåmyran, Ång</t>
+          <t>Bodmyran, Bodmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582380</v>
+        <v>582561</v>
       </c>
       <c r="R10" t="n">
-        <v>7040762</v>
+        <v>7040646</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1684,7 +1679,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1694,7 +1689,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1709,12 +1709,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1838,10 +1838,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123272584</v>
+        <v>123273924</v>
       </c>
       <c r="B12" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1854,34 +1854,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bodmyran, Bodmyran, Ång</t>
+          <t>Kilåmyran, Kilåmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582561</v>
+        <v>582401</v>
       </c>
       <c r="R12" t="n">
-        <v>7040650</v>
+        <v>7040750</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
